--- a/Data/Home/Context.Brightness.xlsx
+++ b/Data/Home/Context.Brightness.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709245321</v>
+        <v>1711840629</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709251627</v>
+        <v>1711849071</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709259011</v>
+        <v>1711855361</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709280167</v>
+        <v>1711880558</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709281590</v>
+        <v>1711882174</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709289673</v>
+        <v>1711887627</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709240697</v>
+        <v>1711923679</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709245082</v>
+        <v>1711929361</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709251533</v>
+        <v>1711938041</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709269383</v>
+        <v>1711964899</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709271446</v>
+        <v>1711967281</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709278458</v>
+        <v>1711976336</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709328480</v>
+        <v>1712009648</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709334694</v>
+        <v>1712015605</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709339780</v>
+        <v>1712024606</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709358984</v>
+        <v>1712051182</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709360022</v>
+        <v>1712053277</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709364019</v>
+        <v>1712063901</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709414268</v>
+        <v>1712095679</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709420580</v>
+        <v>1712101691</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709425281</v>
+        <v>1712110775</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709444533</v>
+        <v>1712135238</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709445737</v>
+        <v>1712137201</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709449775</v>
+        <v>1712147108</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709498196</v>
+        <v>1712181251</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709502931</v>
+        <v>1712187708</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1331,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709509205</v>
+        <v>1712196365</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709532345</v>
+        <v>1712221928</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709535126</v>
+        <v>1712223902</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709544127</v>
+        <v>1712232496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709584224</v>
+        <v>1712268764</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709589532</v>
+        <v>1712274833</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709596764</v>
+        <v>1712283190</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709619253</v>
+        <v>1712310008</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709621727</v>
+        <v>1712312384</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1628,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709629467</v>
+        <v>1712321885</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1661,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709671936</v>
+        <v>1712358161</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709677037</v>
+        <v>1712366611</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709684211</v>
+        <v>1712372142</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1760,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709705264</v>
+        <v>1712396388</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709706741</v>
+        <v>1712397779</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709714043</v>
+        <v>1712403109</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1859,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709758030</v>
+        <v>1712441645</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709763241</v>
+        <v>1712447807</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709769830</v>
+        <v>1712456369</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709788251</v>
+        <v>1712483076</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709789778</v>
+        <v>1712485223</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709796609</v>
+        <v>1712495195</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709844857</v>
+        <v>1712530191</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709849548</v>
+        <v>1712538282</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709855746</v>
+        <v>1712544178</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709873925</v>
+        <v>1712567750</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709875543</v>
+        <v>1712569098</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709883046</v>
+        <v>1712574182</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709932843</v>
+        <v>1712613729</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709938051</v>
+        <v>1712619708</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709944729</v>
+        <v>1712628839</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709965146</v>
+        <v>1712656306</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2387,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709967620</v>
+        <v>1712658196</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709976794</v>
+        <v>1712668031</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710017294</v>
+        <v>1712700344</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2486,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710022313</v>
+        <v>1712706412</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710028934</v>
+        <v>1712715170</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710048917</v>
+        <v>1712742128</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2585,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710050882</v>
+        <v>1712744319</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2618,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710058299</v>
+        <v>1712754677</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710104077</v>
+        <v>1712786874</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710108666</v>
+        <v>1712793200</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2717,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710115408</v>
+        <v>1712801394</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2750,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710136333</v>
+        <v>1712827066</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2783,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710137926</v>
+        <v>1712829454</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710147121</v>
+        <v>1712839661</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2849,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710195321</v>
+        <v>1712873070</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2882,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710202704</v>
+        <v>1712878798</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2915,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710208435</v>
+        <v>1712887288</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710229047</v>
+        <v>1712913966</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +2981,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710230472</v>
+        <v>1712916779</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3014,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710234500</v>
+        <v>1712925474</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3047,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710278645</v>
+        <v>1712962019</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3080,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710284433</v>
+        <v>1712970414</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3113,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710292349</v>
+        <v>1712976366</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3146,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710316109</v>
+        <v>1713000746</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3179,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710318777</v>
+        <v>1713002166</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3212,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710324489</v>
+        <v>1713007264</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710362409</v>
+        <v>1713045564</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3278,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710367845</v>
+        <v>1713052173</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710375294</v>
+        <v>1713060365</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710395550</v>
+        <v>1713086255</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3377,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710398147</v>
+        <v>1713089202</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3410,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710406211</v>
+        <v>1713100689</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3443,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710452508</v>
+        <v>1713134155</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710458043</v>
+        <v>1713142766</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710464972</v>
+        <v>1713148740</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710485079</v>
+        <v>1713172189</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710486400</v>
+        <v>1713173739</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710494129</v>
+        <v>1713178993</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710537724</v>
+        <v>1713219411</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710543646</v>
+        <v>1713226013</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710548014</v>
+        <v>1713235047</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710565142</v>
+        <v>1713261826</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3773,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710566210</v>
+        <v>1713265019</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3806,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710569900</v>
+        <v>1713275911</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3839,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710623489</v>
+        <v>1713305397</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3872,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710627828</v>
+        <v>1713311849</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3905,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710633823</v>
+        <v>1713320882</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710653933</v>
+        <v>1713346581</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710655920</v>
+        <v>1713348516</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4004,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710663221</v>
+        <v>1713357273</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4037,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710709758</v>
+        <v>1713393392</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710715154</v>
+        <v>1713401689</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4103,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710722782</v>
+        <v>1713408021</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4136,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710744971</v>
+        <v>1713432046</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4169,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710746528</v>
+        <v>1713433412</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710754269</v>
+        <v>1713437717</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4235,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710796060</v>
+        <v>1713478838</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4268,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710801185</v>
+        <v>1713484870</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710808157</v>
+        <v>1713492816</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4334,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710829735</v>
+        <v>1713518414</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710831702</v>
+        <v>1713521257</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710839586</v>
+        <v>1713531771</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710880361</v>
+        <v>1713565572</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4466,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710885006</v>
+        <v>1713572071</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4499,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710892155</v>
+        <v>1713580810</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710914697</v>
+        <v>1713607882</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710917312</v>
+        <v>1713610836</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4598,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710925368</v>
+        <v>1713621557</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4631,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710968548</v>
+        <v>1713650077</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4664,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710973370</v>
+        <v>1713655950</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4697,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710980110</v>
+        <v>1713664338</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4730,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711001243</v>
+        <v>1713688977</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4763,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711002984</v>
+        <v>1713691058</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4796,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711010049</v>
+        <v>1713700109</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4829,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711054169</v>
+        <v>1713736559</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4862,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711059542</v>
+        <v>1713742452</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4895,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711066839</v>
+        <v>1713750962</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4928,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711086829</v>
+        <v>1713776619</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4961,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711088677</v>
+        <v>1713778478</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +4994,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711095380</v>
+        <v>1713786471</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711141725</v>
+        <v>1713823216</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5060,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711146722</v>
+        <v>1713829501</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5093,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711153221</v>
+        <v>1713837711</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5126,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711173746</v>
+        <v>1713863556</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5159,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711175492</v>
+        <v>1713866070</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5192,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711181772</v>
+        <v>1713874860</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5225,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711229684</v>
+        <v>1713911162</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5258,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711235066</v>
+        <v>1713919586</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5291,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5310,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711242306</v>
+        <v>1713926199</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5324,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5343,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711265217</v>
+        <v>1713950493</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5357,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5376,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711267767</v>
+        <v>1713951931</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5390,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5409,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711277001</v>
+        <v>1713957617</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5423,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5442,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711315232</v>
+        <v>1713998749</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5456,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711320245</v>
+        <v>1714006944</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5489,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5508,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711327406</v>
+        <v>1714013028</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5522,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5541,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711350387</v>
+        <v>1714036114</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5555,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5574,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711352476</v>
+        <v>1714037470</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5588,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5607,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711359992</v>
+        <v>1714042608</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5621,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5640,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711404488</v>
+        <v>1714082459</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5654,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5673,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711410811</v>
+        <v>1714088973</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5687,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5706,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711419888</v>
+        <v>1714097994</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5720,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5739,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711448358</v>
+        <v>1714125357</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5753,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5772,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711451346</v>
+        <v>1714127618</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5786,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5805,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711461711</v>
+        <v>1714137557</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5819,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5838,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711491086</v>
+        <v>1714168982</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5852,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5871,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711497305</v>
+        <v>1714175120</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5885,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5904,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711506920</v>
+        <v>1714184011</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +5918,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5937,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711536681</v>
+        <v>1714211520</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +5951,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +5970,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711538990</v>
+        <v>1714214032</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +5984,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6003,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711547788</v>
+        <v>1714225100</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6017,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6036,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711577496</v>
+        <v>1714256281</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6050,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6069,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711583524</v>
+        <v>1714262676</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6083,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6102,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711592309</v>
+        <v>1714271906</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6116,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6135,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711621136</v>
+        <v>1714298112</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6149,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6168,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711623915</v>
+        <v>1714300916</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6182,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6201,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711633804</v>
+        <v>1714313043</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6215,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
